--- a/artfynd/A 5027-2023 artfynd.xlsx
+++ b/artfynd/A 5027-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>118222866</v>
       </c>
       <c r="B2" t="n">
-        <v>57287</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,12 +780,7 @@
         <v>118222557</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +867,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -892,12 +882,7 @@
         <v>118222730</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +969,7 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -999,12 +984,7 @@
         <v>118222736</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1071,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">

--- a/artfynd/A 5027-2023 artfynd.xlsx
+++ b/artfynd/A 5027-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118222866</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>57726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>118222557</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>118222730</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>118222736</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>57726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 5027-2023 artfynd.xlsx
+++ b/artfynd/A 5027-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118222866</v>
       </c>
       <c r="B2" t="n">
-        <v>57726</v>
+        <v>57729</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>118222557</v>
       </c>
       <c r="B3" t="n">
-        <v>57726</v>
+        <v>57729</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>118222730</v>
       </c>
       <c r="B4" t="n">
-        <v>57726</v>
+        <v>57729</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>118222736</v>
       </c>
       <c r="B5" t="n">
-        <v>57726</v>
+        <v>57729</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 5027-2023 artfynd.xlsx
+++ b/artfynd/A 5027-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118222866</v>
+        <v>118222557</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>57942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490535</v>
+        <v>490482</v>
       </c>
       <c r="R2" t="n">
-        <v>6297784</v>
+        <v>6297791</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,21 +770,21 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Emil Lundahl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118222557</v>
+        <v>118222730</v>
       </c>
       <c r="B3" t="n">
-        <v>57730</v>
+        <v>57942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490482</v>
+        <v>490466</v>
       </c>
       <c r="R3" t="n">
-        <v>6297791</v>
+        <v>6297866</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,14 +879,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118222730</v>
+        <v>118222736</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>57942</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490466</v>
+        <v>490549</v>
       </c>
       <c r="R4" t="n">
-        <v>6297866</v>
+        <v>6297805</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,14 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118222736</v>
+        <v>118222866</v>
       </c>
       <c r="B5" t="n">
-        <v>57730</v>
+        <v>57942</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490549</v>
+        <v>490535</v>
       </c>
       <c r="R5" t="n">
-        <v>6297805</v>
+        <v>6297784</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,39 +1076,34 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emil Lundahl</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118222550</v>
+        <v>118222553</v>
       </c>
       <c r="B6" t="n">
-        <v>57993</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>102626</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1119,7 +1114,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490477</v>
+        <v>490474</v>
       </c>
       <c r="R6" t="n">
-        <v>6297778</v>
+        <v>6297775</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,7 +1173,7 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -1190,32 +1185,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118223257</v>
+        <v>118222729</v>
       </c>
       <c r="B7" t="n">
-        <v>57993</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>102626</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1226,7 +1216,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490462</v>
+        <v>490504</v>
       </c>
       <c r="R7" t="n">
-        <v>6297863</v>
+        <v>6297897</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1265,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,27 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Emil Lundahl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118222553</v>
+        <v>118223267</v>
       </c>
       <c r="B8" t="n">
-        <v>57385</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102626</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490474</v>
+        <v>490606</v>
       </c>
       <c r="R8" t="n">
-        <v>6297775</v>
+        <v>6297735</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1372,12 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,15 +1377,321 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118222550</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norra Rinkaby, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>490477</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6297778</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tävelsås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
           <t>Emil Lundahl</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118223257</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norra Rinkaby, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>490462</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6297863</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tävelsås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118222539</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norra Rinkaby, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>490319</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6297800</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tävelsås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emil Lundahl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5027-2023 artfynd.xlsx
+++ b/artfynd/A 5027-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118222557</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118222730</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118222736</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118222866</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118222553</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118222729</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118223267</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118222550</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118223257</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,8 +1742,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118222539</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>